--- a/Сценарий 3_generated.xlsx
+++ b/Сценарий 3_generated.xlsx
@@ -1058,7 +1058,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="216">
+  <cellXfs count="220">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1592,6 +1592,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="31" fillId="15" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="31" fillId="16" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="32" fillId="15" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="33" fillId="16" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="33" fillId="15" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="14" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -32367,7 +32379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J148"/>
+  <dimension ref="A1:J158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="161" min="1" max="1"/>
@@ -32386,7 +32398,7 @@
       <c r="A1" s="188" t="inlineStr"/>
       <c r="B1" s="189" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Total PN</t>
         </is>
       </c>
       <c r="C1" s="190" t="inlineStr">
@@ -32496,10 +32508,10 @@
         <v>0</v>
       </c>
       <c r="I3" s="196" t="n">
-        <v>0.05</v>
+        <v>0.015</v>
       </c>
       <c r="J3" s="196" t="n">
-        <v>0.1038461538461539</v>
+        <v>0.06884615384615385</v>
       </c>
     </row>
     <row r="4">
@@ -32556,13 +32568,13 @@
         <v>0</v>
       </c>
       <c r="E5" s="195" t="n">
-        <v>0.1</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F5" s="195" t="n">
         <v>0.09000000000000001</v>
       </c>
       <c r="G5" s="195" t="n">
-        <v>0.05076923076923078</v>
+        <v>0.04846153846153847</v>
       </c>
       <c r="H5" s="195" t="n">
         <v>0</v>
@@ -32571,7 +32583,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="196" t="n">
-        <v>0.05076923076923078</v>
+        <v>0.04846153846153847</v>
       </c>
     </row>
     <row r="6">
@@ -32655,22 +32667,22 @@
         <v>0.27</v>
       </c>
       <c r="E8" s="198" t="n">
-        <v>0.295</v>
+        <v>0.285</v>
       </c>
       <c r="F8" s="198" t="n">
         <v>0.285</v>
       </c>
       <c r="G8" s="198" t="n">
-        <v>0.2778007655851258</v>
+        <v>0.2754930732774335</v>
       </c>
       <c r="H8" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="198" t="n">
-        <v>0.185</v>
+        <v>0.15</v>
       </c>
       <c r="J8" s="198" t="n">
-        <v>0.4628007655851258</v>
+        <v>0.4254930732774335</v>
       </c>
     </row>
     <row r="9"/>
@@ -32679,7 +32691,7 @@
       <c r="A11" s="188" t="inlineStr"/>
       <c r="B11" s="189" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="C11" s="190" t="inlineStr">
@@ -32780,19 +32792,19 @@
         <v>0.1</v>
       </c>
       <c r="F13" s="195" t="n">
-        <v>0.07742890995260657</v>
+        <v>0.1</v>
       </c>
       <c r="G13" s="195" t="n">
-        <v>0.04690120306234048</v>
+        <v>0.05384615384615385</v>
       </c>
       <c r="H13" s="195" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="196" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J13" s="196" t="n">
-        <v>0.04690120306234048</v>
+        <v>0.1038461538461539</v>
       </c>
     </row>
     <row r="14">
@@ -32852,10 +32864,10 @@
         <v>0.1</v>
       </c>
       <c r="F15" s="195" t="n">
-        <v>0.1</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="G15" s="195" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.05076923076923078</v>
       </c>
       <c r="H15" s="195" t="n">
         <v>0</v>
@@ -32864,7 +32876,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="196" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.05076923076923078</v>
       </c>
     </row>
     <row r="16">
@@ -32951,19 +32963,19 @@
         <v>0.295</v>
       </c>
       <c r="F18" s="198" t="n">
-        <v>0.2724289099526066</v>
+        <v>0.285</v>
       </c>
       <c r="G18" s="198" t="n">
-        <v>0.2739327378782355</v>
+        <v>0.2778007655851258</v>
       </c>
       <c r="H18" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="198" t="n">
-        <v>0.135</v>
+        <v>0.185</v>
       </c>
       <c r="J18" s="198" t="n">
-        <v>0.4089327378782355</v>
+        <v>0.4628007655851258</v>
       </c>
     </row>
     <row r="19"/>
@@ -32972,7 +32984,7 @@
       <c r="A21" s="188" t="inlineStr"/>
       <c r="B21" s="189" t="inlineStr">
         <is>
-          <t>Moscow</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C21" s="190" t="inlineStr">
@@ -33073,19 +33085,19 @@
         <v>0.1</v>
       </c>
       <c r="F23" s="195" t="n">
-        <v>0.1</v>
+        <v>0.07742890995260657</v>
       </c>
       <c r="G23" s="195" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.04690120306234048</v>
       </c>
       <c r="H23" s="195" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="196" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J23" s="196" t="n">
-        <v>0.1038461538461539</v>
+        <v>0.04690120306234048</v>
       </c>
     </row>
     <row r="24">
@@ -33142,13 +33154,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="195" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="F25" s="195" t="n">
         <v>0.1</v>
       </c>
       <c r="G25" s="195" t="n">
-        <v>0.05153846153846154</v>
+        <v>0.05384615384615385</v>
       </c>
       <c r="H25" s="195" t="n">
         <v>0</v>
@@ -33157,7 +33169,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="196" t="n">
-        <v>0.05153846153846154</v>
+        <v>0.05384615384615385</v>
       </c>
     </row>
     <row r="26">
@@ -33241,22 +33253,22 @@
         <v>0.27</v>
       </c>
       <c r="E28" s="198" t="n">
-        <v>0.285</v>
+        <v>0.295</v>
       </c>
       <c r="F28" s="198" t="n">
-        <v>0.295</v>
+        <v>0.2724289099526066</v>
       </c>
       <c r="G28" s="198" t="n">
-        <v>0.2785699963543566</v>
+        <v>0.2739327378782355</v>
       </c>
       <c r="H28" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="198" t="n">
-        <v>0.185</v>
+        <v>0.135</v>
       </c>
       <c r="J28" s="198" t="n">
-        <v>0.4635699963543566</v>
+        <v>0.4089327378782355</v>
       </c>
     </row>
     <row r="29"/>
@@ -33265,7 +33277,7 @@
       <c r="A31" s="188" t="inlineStr"/>
       <c r="B31" s="189" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="C31" s="190" t="inlineStr">
@@ -33375,10 +33387,10 @@
         <v>0</v>
       </c>
       <c r="I33" s="196" t="n">
-        <v>0.005000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="J33" s="196" t="n">
-        <v>0.05884615384615385</v>
+        <v>0.1038461538461539</v>
       </c>
     </row>
     <row r="34">
@@ -33435,13 +33447,13 @@
         <v>0</v>
       </c>
       <c r="E35" s="195" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F35" s="195" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="G35" s="195" t="n">
-        <v>0.03769230769230768</v>
+        <v>0.05153846153846154</v>
       </c>
       <c r="H35" s="195" t="n">
         <v>0</v>
@@ -33450,7 +33462,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="196" t="n">
-        <v>0.03769230769230768</v>
+        <v>0.05153846153846154</v>
       </c>
     </row>
     <row r="36">
@@ -33534,22 +33546,22 @@
         <v>0.27</v>
       </c>
       <c r="E38" s="198" t="n">
-        <v>0.265</v>
+        <v>0.285</v>
       </c>
       <c r="F38" s="198" t="n">
-        <v>0.265</v>
+        <v>0.295</v>
       </c>
       <c r="G38" s="198" t="n">
-        <v>0.2647238425082027</v>
+        <v>0.2785699963543566</v>
       </c>
       <c r="H38" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="198" t="n">
-        <v>0.14</v>
+        <v>0.185</v>
       </c>
       <c r="J38" s="198" t="n">
-        <v>0.4047238425082027</v>
+        <v>0.4635699963543566</v>
       </c>
     </row>
     <row r="39"/>
@@ -33558,7 +33570,7 @@
       <c r="A41" s="188" t="inlineStr"/>
       <c r="B41" s="189" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>South</t>
         </is>
       </c>
       <c r="C41" s="190" t="inlineStr">
@@ -33668,10 +33680,10 @@
         <v>0</v>
       </c>
       <c r="I43" s="196" t="n">
-        <v>0.05</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="J43" s="196" t="n">
-        <v>0.1038461538461539</v>
+        <v>0.05884615384615385</v>
       </c>
     </row>
     <row r="44">
@@ -33728,13 +33740,13 @@
         <v>0</v>
       </c>
       <c r="E45" s="195" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F45" s="195" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="G45" s="195" t="n">
-        <v>0.04846153846153847</v>
+        <v>0.03769230769230768</v>
       </c>
       <c r="H45" s="195" t="n">
         <v>0</v>
@@ -33743,7 +33755,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="196" t="n">
-        <v>0.04846153846153847</v>
+        <v>0.03769230769230768</v>
       </c>
     </row>
     <row r="46">
@@ -33827,22 +33839,22 @@
         <v>0.27</v>
       </c>
       <c r="E48" s="198" t="n">
-        <v>0.285</v>
+        <v>0.265</v>
       </c>
       <c r="F48" s="198" t="n">
-        <v>0.285</v>
+        <v>0.265</v>
       </c>
       <c r="G48" s="198" t="n">
-        <v>0.2754930732774335</v>
+        <v>0.2647238425082027</v>
       </c>
       <c r="H48" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="198" t="n">
-        <v>0.185</v>
+        <v>0.14</v>
       </c>
       <c r="J48" s="198" t="n">
-        <v>0.4604930732774335</v>
+        <v>0.4047238425082027</v>
       </c>
     </row>
     <row r="49"/>
@@ -33851,7 +33863,7 @@
       <c r="A51" s="188" t="inlineStr"/>
       <c r="B51" s="189" t="inlineStr">
         <is>
-          <t>Siberia</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="C51" s="190" t="inlineStr">
@@ -33961,10 +33973,10 @@
         <v>0</v>
       </c>
       <c r="I53" s="196" t="n">
-        <v>0.025</v>
+        <v>0.05</v>
       </c>
       <c r="J53" s="196" t="n">
-        <v>0.07884615384615384</v>
+        <v>0.1038461538461539</v>
       </c>
     </row>
     <row r="54">
@@ -34021,13 +34033,13 @@
         <v>0</v>
       </c>
       <c r="E55" s="195" t="n">
-        <v>0.1</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F55" s="195" t="n">
-        <v>0.1</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="G55" s="195" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.04846153846153847</v>
       </c>
       <c r="H55" s="195" t="n">
         <v>0</v>
@@ -34036,7 +34048,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="196" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.04846153846153847</v>
       </c>
     </row>
     <row r="56">
@@ -34120,22 +34132,22 @@
         <v>0.27</v>
       </c>
       <c r="E58" s="198" t="n">
-        <v>0.295</v>
+        <v>0.285</v>
       </c>
       <c r="F58" s="198" t="n">
-        <v>0.295</v>
+        <v>0.285</v>
       </c>
       <c r="G58" s="198" t="n">
-        <v>0.2808776886620489</v>
+        <v>0.2754930732774335</v>
       </c>
       <c r="H58" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="198" t="n">
-        <v>0.16</v>
+        <v>0.185</v>
       </c>
       <c r="J58" s="198" t="n">
-        <v>0.4408776886620489</v>
+        <v>0.4604930732774335</v>
       </c>
     </row>
     <row r="59"/>
@@ -34144,7 +34156,7 @@
       <c r="A61" s="188" t="inlineStr"/>
       <c r="B61" s="189" t="inlineStr">
         <is>
-          <t>Far East</t>
+          <t>Siberia</t>
         </is>
       </c>
       <c r="C61" s="190" t="inlineStr">
@@ -34254,10 +34266,10 @@
         <v>0</v>
       </c>
       <c r="I63" s="196" t="n">
-        <v>0.05</v>
+        <v>0.025</v>
       </c>
       <c r="J63" s="196" t="n">
-        <v>0.1038461538461539</v>
+        <v>0.07884615384615384</v>
       </c>
     </row>
     <row r="64">
@@ -34314,13 +34326,13 @@
         <v>0</v>
       </c>
       <c r="E65" s="195" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="F65" s="195" t="n">
         <v>0.1</v>
       </c>
       <c r="G65" s="195" t="n">
-        <v>0.05153846153846154</v>
+        <v>0.05384615384615385</v>
       </c>
       <c r="H65" s="195" t="n">
         <v>0</v>
@@ -34329,7 +34341,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="196" t="n">
-        <v>0.05153846153846154</v>
+        <v>0.05384615384615385</v>
       </c>
     </row>
     <row r="66">
@@ -34413,22 +34425,22 @@
         <v>0.27</v>
       </c>
       <c r="E68" s="198" t="n">
-        <v>0.285</v>
+        <v>0.295</v>
       </c>
       <c r="F68" s="198" t="n">
         <v>0.295</v>
       </c>
       <c r="G68" s="198" t="n">
-        <v>0.2785699963543566</v>
+        <v>0.2808776886620489</v>
       </c>
       <c r="H68" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I68" s="198" t="n">
-        <v>0.185</v>
+        <v>0.16</v>
       </c>
       <c r="J68" s="198" t="n">
-        <v>0.4635699963543566</v>
+        <v>0.4408776886620489</v>
       </c>
     </row>
     <row r="69"/>
@@ -34437,7 +34449,7 @@
       <c r="A71" s="188" t="inlineStr"/>
       <c r="B71" s="189" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>Far East</t>
         </is>
       </c>
       <c r="C71" s="190" t="inlineStr">
@@ -34535,22 +34547,22 @@
         <v>0</v>
       </c>
       <c r="E73" s="195" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F73" s="195" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G73" s="195" t="n">
-        <v>0</v>
+        <v>0.05384615384615385</v>
       </c>
       <c r="H73" s="195" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="196" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J73" s="196" t="n">
-        <v>0</v>
+        <v>0.1038461538461539</v>
       </c>
     </row>
     <row r="74">
@@ -34607,13 +34619,13 @@
         <v>0</v>
       </c>
       <c r="E75" s="195" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F75" s="195" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="G75" s="195" t="n">
-        <v>0.03692307692307693</v>
+        <v>0.05153846153846154</v>
       </c>
       <c r="H75" s="195" t="n">
         <v>0</v>
@@ -34622,7 +34634,7 @@
         <v>0</v>
       </c>
       <c r="J75" s="196" t="n">
-        <v>0.03692307692307693</v>
+        <v>0.05153846153846154</v>
       </c>
     </row>
     <row r="76">
@@ -34706,22 +34718,22 @@
         <v>0.27</v>
       </c>
       <c r="E78" s="198" t="n">
-        <v>0.175</v>
+        <v>0.285</v>
       </c>
       <c r="F78" s="198" t="n">
-        <v>0.155</v>
+        <v>0.295</v>
       </c>
       <c r="G78" s="198" t="n">
-        <v>0.2101084578928181</v>
+        <v>0.2785699963543566</v>
       </c>
       <c r="H78" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I78" s="198" t="n">
-        <v>0.135</v>
+        <v>0.185</v>
       </c>
       <c r="J78" s="198" t="n">
-        <v>0.3451084578928181</v>
+        <v>0.4635699963543566</v>
       </c>
     </row>
     <row r="79"/>
@@ -34730,7 +34742,7 @@
       <c r="A81" s="188" t="inlineStr"/>
       <c r="B81" s="189" t="inlineStr">
         <is>
-          <t>D-Com</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="C81" s="190" t="inlineStr">
@@ -34828,13 +34840,13 @@
         <v>0</v>
       </c>
       <c r="E83" s="195" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F83" s="195" t="n">
-        <v>0.08507109004739344</v>
+        <v>0</v>
       </c>
       <c r="G83" s="195" t="n">
-        <v>0.04925264309150568</v>
+        <v>0</v>
       </c>
       <c r="H83" s="195" t="n">
         <v>0</v>
@@ -34843,7 +34855,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="196" t="n">
-        <v>0.04925264309150568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -34900,13 +34912,13 @@
         <v>0</v>
       </c>
       <c r="E85" s="195" t="n">
-        <v>0</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="F85" s="195" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G85" s="195" t="n">
-        <v>0.006153846153846155</v>
+        <v>0.03692307692307693</v>
       </c>
       <c r="H85" s="195" t="n">
         <v>0</v>
@@ -34915,7 +34927,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="196" t="n">
-        <v>0.006153846153846155</v>
+        <v>0.03692307692307693</v>
       </c>
     </row>
     <row r="86">
@@ -34999,13 +35011,13 @@
         <v>0.27</v>
       </c>
       <c r="E88" s="198" t="n">
-        <v>0.195</v>
+        <v>0.175</v>
       </c>
       <c r="F88" s="198" t="n">
-        <v>0.2000710900473934</v>
+        <v>0.155</v>
       </c>
       <c r="G88" s="198" t="n">
-        <v>0.228591870215093</v>
+        <v>0.2101084578928181</v>
       </c>
       <c r="H88" s="198" t="n">
         <v>0</v>
@@ -35014,7 +35026,7 @@
         <v>0.135</v>
       </c>
       <c r="J88" s="198" t="n">
-        <v>0.363591870215093</v>
+        <v>0.3451084578928181</v>
       </c>
     </row>
     <row r="89"/>
@@ -35023,7 +35035,7 @@
       <c r="A91" s="188" t="inlineStr"/>
       <c r="B91" s="189" t="inlineStr">
         <is>
-          <t>Любимчик 2.0</t>
+          <t>D-Com</t>
         </is>
       </c>
       <c r="C91" s="190" t="inlineStr">
@@ -35124,19 +35136,19 @@
         <v>0.1</v>
       </c>
       <c r="F93" s="195" t="n">
-        <v>0.1</v>
+        <v>0.08507109004739344</v>
       </c>
       <c r="G93" s="195" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.04925264309150568</v>
       </c>
       <c r="H93" s="195" t="n">
         <v>0</v>
       </c>
       <c r="I93" s="196" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J93" s="196" t="n">
-        <v>0.1038461538461539</v>
+        <v>0.04925264309150568</v>
       </c>
     </row>
     <row r="94">
@@ -35196,10 +35208,10 @@
         <v>0</v>
       </c>
       <c r="F95" s="195" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G95" s="195" t="n">
-        <v>0</v>
+        <v>0.006153846153846155</v>
       </c>
       <c r="H95" s="195" t="n">
         <v>0</v>
@@ -35208,7 +35220,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="196" t="n">
-        <v>0</v>
+        <v>0.006153846153846155</v>
       </c>
     </row>
     <row r="96">
@@ -35295,19 +35307,19 @@
         <v>0.195</v>
       </c>
       <c r="F98" s="198" t="n">
-        <v>0.195</v>
+        <v>0.2000710900473934</v>
       </c>
       <c r="G98" s="198" t="n">
-        <v>0.227031534815895</v>
+        <v>0.228591870215093</v>
       </c>
       <c r="H98" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I98" s="198" t="n">
-        <v>0.185</v>
+        <v>0.135</v>
       </c>
       <c r="J98" s="198" t="n">
-        <v>0.4120315348158951</v>
+        <v>0.363591870215093</v>
       </c>
     </row>
     <row r="99"/>
@@ -35316,7 +35328,7 @@
       <c r="A101" s="188" t="inlineStr"/>
       <c r="B101" s="189" t="inlineStr">
         <is>
-          <t>X5</t>
+          <t>Любимчик 2.0</t>
         </is>
       </c>
       <c r="C101" s="190" t="inlineStr">
@@ -35426,10 +35438,10 @@
         <v>0</v>
       </c>
       <c r="I103" s="196" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="J103" s="196" t="n">
-        <v>0.08384615384615385</v>
+        <v>0.1038461538461539</v>
       </c>
     </row>
     <row r="104">
@@ -35486,13 +35498,13 @@
         <v>0</v>
       </c>
       <c r="E105" s="195" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F105" s="195" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G105" s="195" t="n">
-        <v>0.05384615384615385</v>
+        <v>0</v>
       </c>
       <c r="H105" s="195" t="n">
         <v>0</v>
@@ -35501,7 +35513,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="196" t="n">
-        <v>0.05384615384615385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -35585,22 +35597,22 @@
         <v>0.27</v>
       </c>
       <c r="E108" s="198" t="n">
-        <v>0.295</v>
+        <v>0.195</v>
       </c>
       <c r="F108" s="198" t="n">
-        <v>0.295</v>
+        <v>0.195</v>
       </c>
       <c r="G108" s="198" t="n">
-        <v>0.2808776886620489</v>
+        <v>0.227031534815895</v>
       </c>
       <c r="H108" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I108" s="198" t="n">
-        <v>0.165</v>
+        <v>0.185</v>
       </c>
       <c r="J108" s="198" t="n">
-        <v>0.4458776886620489</v>
+        <v>0.4120315348158951</v>
       </c>
     </row>
     <row r="109"/>
@@ -35609,7 +35621,7 @@
       <c r="A111" s="188" t="inlineStr"/>
       <c r="B111" s="189" t="inlineStr">
         <is>
-          <t>Magnit &amp; Dixy</t>
+          <t>X5</t>
         </is>
       </c>
       <c r="C111" s="190" t="inlineStr">
@@ -35707,22 +35719,22 @@
         <v>0</v>
       </c>
       <c r="E113" s="195" t="n">
-        <v>0.08507109004739344</v>
+        <v>0.1</v>
       </c>
       <c r="F113" s="195" t="n">
-        <v>0.04739336492891005</v>
+        <v>0.1</v>
       </c>
       <c r="G113" s="195" t="n">
-        <v>0.03421436383521696</v>
+        <v>0.05384615384615385</v>
       </c>
       <c r="H113" s="195" t="n">
         <v>0</v>
       </c>
       <c r="I113" s="196" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J113" s="196" t="n">
-        <v>0.03421436383521696</v>
+        <v>0.08384615384615385</v>
       </c>
     </row>
     <row r="114">
@@ -35779,13 +35791,13 @@
         <v>0</v>
       </c>
       <c r="E115" s="195" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="F115" s="195" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.1</v>
       </c>
       <c r="G115" s="195" t="n">
-        <v>0.04538461538461539</v>
+        <v>0.05384615384615385</v>
       </c>
       <c r="H115" s="195" t="n">
         <v>0</v>
@@ -35794,7 +35806,7 @@
         <v>0</v>
       </c>
       <c r="J115" s="196" t="n">
-        <v>0.04538461538461539</v>
+        <v>0.05384615384615385</v>
       </c>
     </row>
     <row r="116">
@@ -35878,22 +35890,22 @@
         <v>0.27</v>
       </c>
       <c r="E118" s="198" t="n">
-        <v>0.2700710900473934</v>
+        <v>0.295</v>
       </c>
       <c r="F118" s="198" t="n">
-        <v>0.2223933649289101</v>
+        <v>0.295</v>
       </c>
       <c r="G118" s="198" t="n">
-        <v>0.2527843601895735</v>
+        <v>0.2808776886620489</v>
       </c>
       <c r="H118" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I118" s="198" t="n">
-        <v>0.135</v>
+        <v>0.165</v>
       </c>
       <c r="J118" s="198" t="n">
-        <v>0.3877843601895735</v>
+        <v>0.4458776886620489</v>
       </c>
     </row>
     <row r="119"/>
@@ -35902,7 +35914,7 @@
       <c r="A121" s="188" t="inlineStr"/>
       <c r="B121" s="189" t="inlineStr">
         <is>
-          <t>Lenta</t>
+          <t>Magnit &amp; Dixy</t>
         </is>
       </c>
       <c r="C121" s="190" t="inlineStr">
@@ -36000,22 +36012,22 @@
         <v>0</v>
       </c>
       <c r="E123" s="195" t="n">
-        <v>0.1</v>
+        <v>0.08507109004739344</v>
       </c>
       <c r="F123" s="195" t="n">
-        <v>0.1</v>
+        <v>0.04739336492891005</v>
       </c>
       <c r="G123" s="195" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.03421436383521696</v>
       </c>
       <c r="H123" s="195" t="n">
         <v>0</v>
       </c>
       <c r="I123" s="196" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J123" s="196" t="n">
-        <v>0.1038461538461539</v>
+        <v>0.03421436383521696</v>
       </c>
     </row>
     <row r="124">
@@ -36072,13 +36084,13 @@
         <v>0</v>
       </c>
       <c r="E125" s="195" t="n">
-        <v>0.1</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F125" s="195" t="n">
-        <v>0.1</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="G125" s="195" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.04538461538461539</v>
       </c>
       <c r="H125" s="195" t="n">
         <v>0</v>
@@ -36087,7 +36099,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="196" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.04538461538461539</v>
       </c>
     </row>
     <row r="126">
@@ -36171,22 +36183,22 @@
         <v>0.27</v>
       </c>
       <c r="E128" s="198" t="n">
-        <v>0.295</v>
+        <v>0.2700710900473934</v>
       </c>
       <c r="F128" s="198" t="n">
-        <v>0.295</v>
+        <v>0.2223933649289101</v>
       </c>
       <c r="G128" s="198" t="n">
-        <v>0.2808776886620489</v>
+        <v>0.2527843601895735</v>
       </c>
       <c r="H128" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I128" s="198" t="n">
-        <v>0.185</v>
+        <v>0.135</v>
       </c>
       <c r="J128" s="198" t="n">
-        <v>0.4658776886620489</v>
+        <v>0.3877843601895735</v>
       </c>
     </row>
     <row r="129"/>
@@ -36195,7 +36207,7 @@
       <c r="A131" s="188" t="inlineStr"/>
       <c r="B131" s="189" t="inlineStr">
         <is>
-          <t>HMs</t>
+          <t>Lenta</t>
         </is>
       </c>
       <c r="C131" s="190" t="inlineStr">
@@ -36296,19 +36308,19 @@
         <v>0.1</v>
       </c>
       <c r="F133" s="195" t="n">
-        <v>0.07742890995260657</v>
+        <v>0.1</v>
       </c>
       <c r="G133" s="195" t="n">
-        <v>0.04690120306234048</v>
+        <v>0.05384615384615385</v>
       </c>
       <c r="H133" s="195" t="n">
         <v>0</v>
       </c>
       <c r="I133" s="196" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J133" s="196" t="n">
-        <v>0.04690120306234048</v>
+        <v>0.1038461538461539</v>
       </c>
     </row>
     <row r="134">
@@ -36467,19 +36479,19 @@
         <v>0.295</v>
       </c>
       <c r="F138" s="198" t="n">
-        <v>0.2724289099526066</v>
+        <v>0.295</v>
       </c>
       <c r="G138" s="198" t="n">
-        <v>0.2739327378782355</v>
+        <v>0.2808776886620489</v>
       </c>
       <c r="H138" s="198" t="n">
         <v>0</v>
       </c>
       <c r="I138" s="198" t="n">
-        <v>0.135</v>
+        <v>0.185</v>
       </c>
       <c r="J138" s="198" t="n">
-        <v>0.4089327378782355</v>
+        <v>0.4658776886620489</v>
       </c>
     </row>
     <row r="139"/>
@@ -36488,7 +36500,7 @@
       <c r="A141" s="188" t="inlineStr"/>
       <c r="B141" s="189" t="inlineStr">
         <is>
-          <t>OMNI</t>
+          <t>HMs</t>
         </is>
       </c>
       <c r="C141" s="190" t="inlineStr">
@@ -36589,19 +36601,19 @@
         <v>0.1</v>
       </c>
       <c r="F143" s="195" t="n">
-        <v>0.1</v>
+        <v>0.07742890995260657</v>
       </c>
       <c r="G143" s="195" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.04690120306234048</v>
       </c>
       <c r="H143" s="195" t="n">
         <v>0</v>
       </c>
       <c r="I143" s="196" t="n">
-        <v>0.005000000000000001</v>
+        <v>0</v>
       </c>
       <c r="J143" s="196" t="n">
-        <v>0.05884615384615385</v>
+        <v>0.04690120306234048</v>
       </c>
     </row>
     <row r="144">
@@ -36760,18 +36772,311 @@
         <v>0.295</v>
       </c>
       <c r="F148" s="198" t="n">
+        <v>0.2724289099526066</v>
+      </c>
+      <c r="G148" s="198" t="n">
+        <v>0.2739327378782355</v>
+      </c>
+      <c r="H148" s="198" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" s="198" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="J148" s="198" t="n">
+        <v>0.4089327378782355</v>
+      </c>
+    </row>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151">
+      <c r="A151" s="188" t="inlineStr"/>
+      <c r="B151" s="189" t="inlineStr">
+        <is>
+          <t>OMNI</t>
+        </is>
+      </c>
+      <c r="C151" s="190" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D151" s="190" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E151" s="190" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F151" s="190" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="G151" s="190" t="inlineStr">
+        <is>
+          <t>FY(100%)</t>
+        </is>
+      </c>
+      <c r="H151" s="190" t="inlineStr">
+        <is>
+          <t>Add Bonus</t>
+        </is>
+      </c>
+      <c r="I151" s="190" t="inlineStr">
+        <is>
+          <t>FY (200%)</t>
+        </is>
+      </c>
+      <c r="J151" s="190" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="191" t="inlineStr">
+        <is>
+          <t>KPI 1</t>
+        </is>
+      </c>
+      <c r="B152" s="191" t="inlineStr">
+        <is>
+          <t>NSV Total</t>
+        </is>
+      </c>
+      <c r="C152" s="192" t="n">
+        <v>0.1388033175355451</v>
+      </c>
+      <c r="D152" s="192" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E152" s="192" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F152" s="192" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G152" s="192" t="n">
+        <v>0.09356999635435656</v>
+      </c>
+      <c r="H152" s="192" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" s="193" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J152" s="193" t="n">
+        <v>0.1235699963543566</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="194" t="inlineStr">
+        <is>
+          <t>KPI 2</t>
+        </is>
+      </c>
+      <c r="B153" s="194" t="inlineStr">
+        <is>
+          <t>NSV Team</t>
+        </is>
+      </c>
+      <c r="C153" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" s="195" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F153" s="195" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G153" s="195" t="n">
+        <v>0.05384615384615385</v>
+      </c>
+      <c r="H153" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" s="196" t="n">
+        <v>0.005000000000000001</v>
+      </c>
+      <c r="J153" s="196" t="n">
+        <v>0.05884615384615385</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="191" t="inlineStr">
+        <is>
+          <t>KPI 3</t>
+        </is>
+      </c>
+      <c r="B154" s="191" t="inlineStr">
+        <is>
+          <t>LSV/t Total</t>
+        </is>
+      </c>
+      <c r="C154" s="192" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D154" s="192" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E154" s="192" t="n">
+        <v>0.04500000000000001</v>
+      </c>
+      <c r="F154" s="192" t="n">
+        <v>0.04500000000000001</v>
+      </c>
+      <c r="G154" s="192" t="n">
+        <v>0.07961538461538462</v>
+      </c>
+      <c r="H154" s="192" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" s="193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" s="193" t="n">
+        <v>0.07961538461538462</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="194" t="inlineStr">
+        <is>
+          <t>KPI 4</t>
+        </is>
+      </c>
+      <c r="B155" s="194" t="inlineStr">
+        <is>
+          <t>LSV/t Team</t>
+        </is>
+      </c>
+      <c r="C155" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" s="195" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F155" s="195" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G155" s="195" t="n">
+        <v>0.05384615384615385</v>
+      </c>
+      <c r="H155" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" s="196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" s="196" t="n">
+        <v>0.05384615384615385</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="191" t="inlineStr">
+        <is>
+          <t>KPI 5</t>
+        </is>
+      </c>
+      <c r="B156" s="191" t="inlineStr">
+        <is>
+          <t>Earnings</t>
+        </is>
+      </c>
+      <c r="C156" s="192" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" s="192" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" s="192" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" s="192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" s="192" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" s="193" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="J156" s="193" t="n">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="194" t="inlineStr">
+        <is>
+          <t>KPI 6</t>
+        </is>
+      </c>
+      <c r="B157" s="194" t="inlineStr">
+        <is>
+          <t>Nsv Prem + Total</t>
+        </is>
+      </c>
+      <c r="C157" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" s="196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" s="196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="197" t="inlineStr"/>
+      <c r="C158" s="198" t="n">
+        <v>0.2588033175355451</v>
+      </c>
+      <c r="D158" s="198" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E158" s="198" t="n">
         <v>0.295</v>
       </c>
-      <c r="G148" s="198" t="n">
+      <c r="F158" s="198" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="G158" s="198" t="n">
         <v>0.2808776886620489</v>
       </c>
-      <c r="H148" s="198" t="n">
-        <v>0</v>
-      </c>
-      <c r="I148" s="198" t="n">
+      <c r="H158" s="198" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" s="198" t="n">
         <v>0.14</v>
       </c>
-      <c r="J148" s="198" t="n">
+      <c r="J158" s="198" t="n">
         <v>0.4208776886620489</v>
       </c>
     </row>
@@ -36786,7 +37091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="161" min="1" max="1"/>
@@ -37715,49 +38020,96 @@
     </row>
     <row r="19">
       <c r="A19" s="199" t="n"/>
-      <c r="B19" s="211" t="inlineStr">
+      <c r="B19" s="200" t="inlineStr">
         <is>
           <t>Total PN</t>
         </is>
       </c>
-      <c r="C19" s="212" t="n">
+      <c r="C19" s="211" t="n">
         <v>1.012977411325948</v>
       </c>
-      <c r="D19" s="213" t="n">
+      <c r="D19" s="212" t="n">
+        <v>0.05384615384615385</v>
+      </c>
+      <c r="E19" s="213" t="n">
+        <v>0.997896799895361</v>
+      </c>
+      <c r="F19" s="212" t="n">
+        <v>0.04846153846153847</v>
+      </c>
+      <c r="G19" s="213" t="n">
+        <v>0.6576923076923078</v>
+      </c>
+      <c r="H19" s="210" t="n">
+        <v>0.1973076923076923</v>
+      </c>
+      <c r="I19" s="211" t="n">
+        <v>1.012977411325948</v>
+      </c>
+      <c r="J19" s="212" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K19" s="213" t="n">
+        <v>0.997896799895361</v>
+      </c>
+      <c r="L19" s="214" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="199" t="n"/>
+      <c r="N19" s="199" t="n"/>
+      <c r="O19" s="199" t="n"/>
+      <c r="P19" s="199" t="n"/>
+      <c r="Q19" s="211" t="n">
+        <v>1.057692307692308</v>
+      </c>
+      <c r="R19" s="210" t="n">
+        <v>0.3173076923076923</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="215" t="inlineStr">
+        <is>
+          <t>Total Target</t>
+        </is>
+      </c>
+      <c r="C20" s="216" t="n">
+        <v>1.012977411325948</v>
+      </c>
+      <c r="D20" s="217" t="n">
         <v>0.05</v>
       </c>
-      <c r="E19" s="212" t="n">
+      <c r="E20" s="216" t="n">
         <v>0.997896799895361</v>
       </c>
-      <c r="F19" s="213" t="n">
+      <c r="F20" s="217" t="n">
         <v>0.04500000000000001</v>
       </c>
-      <c r="G19" s="212" t="n">
+      <c r="G20" s="216" t="n">
         <v>0.95</v>
       </c>
-      <c r="H19" s="213" t="n">
+      <c r="H20" s="217" t="n">
         <v>0.285</v>
       </c>
-      <c r="I19" s="212" t="n">
+      <c r="I20" s="216" t="n">
         <v>1.012977411325948</v>
       </c>
-      <c r="J19" s="213" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="212" t="n">
+      <c r="J20" s="217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="216" t="n">
         <v>0.997896799895361</v>
       </c>
-      <c r="L19" s="213" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="214" t="n"/>
-      <c r="N19" s="215" t="n"/>
-      <c r="O19" s="214" t="n"/>
-      <c r="P19" s="215" t="n"/>
-      <c r="Q19" s="212" t="n">
+      <c r="L20" s="217" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="218" t="n"/>
+      <c r="N20" s="219" t="n"/>
+      <c r="O20" s="218" t="n"/>
+      <c r="P20" s="219" t="n"/>
+      <c r="Q20" s="216" t="n">
         <v>1.283333333333333</v>
       </c>
-      <c r="R19" s="213" t="n">
+      <c r="R20" s="217" t="n">
         <v>0.385</v>
       </c>
     </row>
@@ -37775,9 +38127,9 @@
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="A4:A10"/>
     <mergeCell ref="M4:M18"/>
-    <mergeCell ref="A11:A18"/>
     <mergeCell ref="O4:O18"/>
     <mergeCell ref="P4:P18"/>
+    <mergeCell ref="A11:A19"/>
     <mergeCell ref="C1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Сценарий 3_generated.xlsx
+++ b/Сценарий 3_generated.xlsx
@@ -3154,19 +3154,19 @@
         </is>
       </c>
       <c r="AM8" s="36" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AN8" s="36" t="n">
-        <v>158.2</v>
+        <v>0</v>
       </c>
       <c r="AO8" s="36" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AP8" s="36" t="n">
-        <v>203.4</v>
+        <v>40.44</v>
       </c>
       <c r="AQ8" s="36" t="n">
-        <v>205</v>
+        <v>41.79</v>
       </c>
     </row>
     <row r="9" ht="15.6" customHeight="1" s="161">
@@ -7562,10 +7562,10 @@
     </row>
     <row r="74">
       <c r="L74" s="27" t="n">
-        <v>126.49</v>
-      </c>
-      <c r="M74" s="79" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M74" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N74" s="29" t="n">
         <v>0</v>
@@ -7574,10 +7574,10 @@
         <v>0</v>
       </c>
       <c r="Q74" s="27" t="n">
-        <v>153.9286</v>
-      </c>
-      <c r="R74" s="79" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R74" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S74" s="29" t="n">
         <v>0</v>
@@ -7586,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="V74" s="27" t="n">
-        <v>194.6</v>
-      </c>
-      <c r="W74" s="79" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="W74" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X74" s="29" t="n">
         <v>0</v>
@@ -7598,7 +7598,7 @@
         <v>0</v>
       </c>
       <c r="AA74" s="27" t="n">
-        <v>197.9082</v>
+        <v>39.34811999999999</v>
       </c>
       <c r="AB74" s="79" t="n">
         <v>1</v>
@@ -7610,7 +7610,7 @@
         <v>0</v>
       </c>
       <c r="AF74" s="27" t="n">
-        <v>203.4</v>
+        <v>40.44</v>
       </c>
       <c r="AG74" s="28" t="n">
         <v>1</v>
@@ -7624,10 +7624,10 @@
     </row>
     <row r="75">
       <c r="L75" s="31" t="n">
-        <v>126.841</v>
-      </c>
-      <c r="M75" s="79" t="n">
-        <v>1.002774922918808</v>
+        <v>0</v>
+      </c>
+      <c r="M75" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N75" s="33" t="n">
         <v>0.1</v>
@@ -7636,10 +7636,10 @@
         <v>0</v>
       </c>
       <c r="Q75" s="31" t="n">
-        <v>154.35574</v>
-      </c>
-      <c r="R75" s="79" t="n">
-        <v>1.002774922918808</v>
+        <v>0</v>
+      </c>
+      <c r="R75" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S75" s="33" t="n">
         <v>0.1</v>
@@ -7648,10 +7648,10 @@
         <v>0</v>
       </c>
       <c r="V75" s="31" t="n">
-        <v>195.14</v>
-      </c>
-      <c r="W75" s="79" t="n">
-        <v>1.002774922918808</v>
+        <v>0</v>
+      </c>
+      <c r="W75" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X75" s="33" t="n">
         <v>0.1</v>
@@ -7660,7 +7660,7 @@
         <v>0</v>
       </c>
       <c r="AA75" s="31" t="n">
-        <v>198.45738</v>
+        <v>39.457308</v>
       </c>
       <c r="AB75" s="79" t="n">
         <v>1.002774922918808</v>
@@ -7672,10 +7672,10 @@
         <v>0</v>
       </c>
       <c r="AF75" s="31" t="n">
-        <v>203.56</v>
+        <v>40.575</v>
       </c>
       <c r="AG75" s="32" t="n">
-        <v>1.0007866273353</v>
+        <v>1.003338278931751</v>
       </c>
       <c r="AH75" s="33" t="n">
         <v>0.1</v>
@@ -7686,10 +7686,10 @@
     </row>
     <row r="76">
       <c r="L76" s="31" t="n">
-        <v>127.192</v>
-      </c>
-      <c r="M76" s="79" t="n">
-        <v>1.005549845837616</v>
+        <v>0</v>
+      </c>
+      <c r="M76" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N76" s="33" t="n">
         <v>0.2</v>
@@ -7698,10 +7698,10 @@
         <v>0</v>
       </c>
       <c r="Q76" s="31" t="n">
-        <v>154.78288</v>
-      </c>
-      <c r="R76" s="79" t="n">
-        <v>1.005549845837616</v>
+        <v>0</v>
+      </c>
+      <c r="R76" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S76" s="33" t="n">
         <v>0.2</v>
@@ -7710,10 +7710,10 @@
         <v>0</v>
       </c>
       <c r="V76" s="31" t="n">
-        <v>195.68</v>
-      </c>
-      <c r="W76" s="79" t="n">
-        <v>1.005549845837616</v>
+        <v>0</v>
+      </c>
+      <c r="W76" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X76" s="33" t="n">
         <v>0.2</v>
@@ -7722,7 +7722,7 @@
         <v>0</v>
       </c>
       <c r="AA76" s="31" t="n">
-        <v>199.00656</v>
+        <v>39.566496</v>
       </c>
       <c r="AB76" s="79" t="n">
         <v>1.005549845837616</v>
@@ -7734,10 +7734,10 @@
         <v>0</v>
       </c>
       <c r="AF76" s="31" t="n">
-        <v>203.72</v>
+        <v>40.70999999999999</v>
       </c>
       <c r="AG76" s="32" t="n">
-        <v>1.0015732546706</v>
+        <v>1.006676557863501</v>
       </c>
       <c r="AH76" s="33" t="n">
         <v>0.2</v>
@@ -7748,10 +7748,10 @@
     </row>
     <row r="77">
       <c r="L77" s="31" t="n">
-        <v>127.543</v>
-      </c>
-      <c r="M77" s="79" t="n">
-        <v>1.008324768756423</v>
+        <v>0</v>
+      </c>
+      <c r="M77" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N77" s="33" t="n">
         <v>0.3</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="Q77" s="31" t="n">
-        <v>155.21002</v>
-      </c>
-      <c r="R77" s="79" t="n">
-        <v>1.008324768756424</v>
+        <v>0</v>
+      </c>
+      <c r="R77" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S77" s="33" t="n">
         <v>0.3</v>
@@ -7772,10 +7772,10 @@
         <v>0</v>
       </c>
       <c r="V77" s="31" t="n">
-        <v>196.22</v>
-      </c>
-      <c r="W77" s="79" t="n">
-        <v>1.008324768756423</v>
+        <v>0</v>
+      </c>
+      <c r="W77" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X77" s="33" t="n">
         <v>0.3</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="AA77" s="31" t="n">
-        <v>199.55574</v>
+        <v>39.675684</v>
       </c>
       <c r="AB77" s="79" t="n">
         <v>1.008324768756424</v>
@@ -7796,10 +7796,10 @@
         <v>0</v>
       </c>
       <c r="AF77" s="31" t="n">
-        <v>203.88</v>
+        <v>40.84499999999999</v>
       </c>
       <c r="AG77" s="32" t="n">
-        <v>1.0023598820059</v>
+        <v>1.010014836795252</v>
       </c>
       <c r="AH77" s="33" t="n">
         <v>0.3</v>
@@ -7810,10 +7810,10 @@
     </row>
     <row r="78">
       <c r="L78" s="31" t="n">
-        <v>127.894</v>
-      </c>
-      <c r="M78" s="79" t="n">
-        <v>1.011099691675231</v>
+        <v>0</v>
+      </c>
+      <c r="M78" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N78" s="33" t="n">
         <v>0.4</v>
@@ -7822,10 +7822,10 @@
         <v>0</v>
       </c>
       <c r="Q78" s="31" t="n">
-        <v>155.63716</v>
-      </c>
-      <c r="R78" s="79" t="n">
-        <v>1.011099691675232</v>
+        <v>0</v>
+      </c>
+      <c r="R78" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S78" s="33" t="n">
         <v>0.4</v>
@@ -7834,10 +7834,10 @@
         <v>0</v>
       </c>
       <c r="V78" s="31" t="n">
-        <v>196.76</v>
-      </c>
-      <c r="W78" s="79" t="n">
-        <v>1.011099691675231</v>
+        <v>0</v>
+      </c>
+      <c r="W78" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X78" s="33" t="n">
         <v>0.4</v>
@@ -7846,10 +7846,10 @@
         <v>0</v>
       </c>
       <c r="AA78" s="31" t="n">
-        <v>200.10492</v>
+        <v>39.78487200000001</v>
       </c>
       <c r="AB78" s="79" t="n">
-        <v>1.011099691675231</v>
+        <v>1.011099691675232</v>
       </c>
       <c r="AC78" s="33" t="n">
         <v>0.4</v>
@@ -7858,10 +7858,10 @@
         <v>0</v>
       </c>
       <c r="AF78" s="31" t="n">
-        <v>204.04</v>
+        <v>40.97999999999999</v>
       </c>
       <c r="AG78" s="32" t="n">
-        <v>1.0031465093412</v>
+        <v>1.013353115727003</v>
       </c>
       <c r="AH78" s="33" t="n">
         <v>0.4</v>
@@ -7872,10 +7872,10 @@
     </row>
     <row r="79">
       <c r="L79" s="31" t="n">
-        <v>128.245</v>
-      </c>
-      <c r="M79" s="79" t="n">
-        <v>1.013874614594039</v>
+        <v>0</v>
+      </c>
+      <c r="M79" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N79" s="33" t="n">
         <v>0.5</v>
@@ -7884,10 +7884,10 @@
         <v>0</v>
       </c>
       <c r="Q79" s="31" t="n">
-        <v>156.0643</v>
-      </c>
-      <c r="R79" s="79" t="n">
-        <v>1.013874614594039</v>
+        <v>0</v>
+      </c>
+      <c r="R79" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S79" s="33" t="n">
         <v>0.5</v>
@@ -7896,10 +7896,10 @@
         <v>0</v>
       </c>
       <c r="V79" s="31" t="n">
-        <v>197.3</v>
-      </c>
-      <c r="W79" s="79" t="n">
-        <v>1.013874614594039</v>
+        <v>0</v>
+      </c>
+      <c r="W79" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X79" s="33" t="n">
         <v>0.5</v>
@@ -7908,7 +7908,7 @@
         <v>0</v>
       </c>
       <c r="AA79" s="31" t="n">
-        <v>200.6541</v>
+        <v>39.89406000000001</v>
       </c>
       <c r="AB79" s="79" t="n">
         <v>1.013874614594039</v>
@@ -7920,10 +7920,10 @@
         <v>0</v>
       </c>
       <c r="AF79" s="31" t="n">
-        <v>204.2</v>
+        <v>41.11499999999999</v>
       </c>
       <c r="AG79" s="32" t="n">
-        <v>1.003933136676499</v>
+        <v>1.016691394658753</v>
       </c>
       <c r="AH79" s="33" t="n">
         <v>0.5</v>
@@ -7934,10 +7934,10 @@
     </row>
     <row r="80">
       <c r="L80" s="31" t="n">
-        <v>128.596</v>
-      </c>
-      <c r="M80" s="79" t="n">
-        <v>1.016649537512847</v>
+        <v>0</v>
+      </c>
+      <c r="M80" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N80" s="33" t="n">
         <v>0.6</v>
@@ -7946,10 +7946,10 @@
         <v>0</v>
       </c>
       <c r="Q80" s="31" t="n">
-        <v>156.49144</v>
-      </c>
-      <c r="R80" s="79" t="n">
-        <v>1.016649537512847</v>
+        <v>0</v>
+      </c>
+      <c r="R80" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S80" s="33" t="n">
         <v>0.6</v>
@@ -7958,10 +7958,10 @@
         <v>0</v>
       </c>
       <c r="V80" s="31" t="n">
-        <v>197.8399999999999</v>
-      </c>
-      <c r="W80" s="79" t="n">
-        <v>1.016649537512847</v>
+        <v>0</v>
+      </c>
+      <c r="W80" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X80" s="33" t="n">
         <v>0.6</v>
@@ -7970,7 +7970,7 @@
         <v>0</v>
       </c>
       <c r="AA80" s="31" t="n">
-        <v>201.20328</v>
+        <v>40.00324800000001</v>
       </c>
       <c r="AB80" s="79" t="n">
         <v>1.016649537512847</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AF80" s="31" t="n">
-        <v>204.36</v>
+        <v>41.24999999999999</v>
       </c>
       <c r="AG80" s="32" t="n">
-        <v>1.004719764011799</v>
+        <v>1.020029673590504</v>
       </c>
       <c r="AH80" s="33" t="n">
         <v>0.6</v>
@@ -7996,10 +7996,10 @@
     </row>
     <row r="81">
       <c r="L81" s="31" t="n">
-        <v>128.947</v>
-      </c>
-      <c r="M81" s="79" t="n">
-        <v>1.019424460431655</v>
+        <v>0</v>
+      </c>
+      <c r="M81" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N81" s="33" t="n">
         <v>0.7</v>
@@ -8008,10 +8008,10 @@
         <v>0</v>
       </c>
       <c r="Q81" s="31" t="n">
-        <v>156.91858</v>
-      </c>
-      <c r="R81" s="79" t="n">
-        <v>1.019424460431655</v>
+        <v>0</v>
+      </c>
+      <c r="R81" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S81" s="33" t="n">
         <v>0.7</v>
@@ -8020,10 +8020,10 @@
         <v>0</v>
       </c>
       <c r="V81" s="31" t="n">
-        <v>198.3799999999999</v>
-      </c>
-      <c r="W81" s="79" t="n">
-        <v>1.019424460431654</v>
+        <v>0</v>
+      </c>
+      <c r="W81" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X81" s="33" t="n">
         <v>0.7</v>
@@ -8032,7 +8032,7 @@
         <v>0</v>
       </c>
       <c r="AA81" s="31" t="n">
-        <v>201.75246</v>
+        <v>40.11243600000002</v>
       </c>
       <c r="AB81" s="79" t="n">
         <v>1.019424460431655</v>
@@ -8044,10 +8044,10 @@
         <v>0</v>
       </c>
       <c r="AF81" s="31" t="n">
-        <v>204.52</v>
+        <v>41.38499999999998</v>
       </c>
       <c r="AG81" s="32" t="n">
-        <v>1.005506391347099</v>
+        <v>1.023367952522255</v>
       </c>
       <c r="AH81" s="33" t="n">
         <v>0.7</v>
@@ -8058,10 +8058,10 @@
     </row>
     <row r="82">
       <c r="L82" s="31" t="n">
-        <v>129.298</v>
-      </c>
-      <c r="M82" s="79" t="n">
-        <v>1.022199383350463</v>
+        <v>0</v>
+      </c>
+      <c r="M82" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N82" s="33" t="n">
         <v>0.8</v>
@@ -8070,10 +8070,10 @@
         <v>0</v>
       </c>
       <c r="Q82" s="31" t="n">
-        <v>157.3457200000001</v>
-      </c>
-      <c r="R82" s="79" t="n">
-        <v>1.022199383350463</v>
+        <v>0</v>
+      </c>
+      <c r="R82" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S82" s="33" t="n">
         <v>0.8</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="V82" s="31" t="n">
-        <v>198.9199999999999</v>
-      </c>
-      <c r="W82" s="79" t="n">
-        <v>1.022199383350462</v>
+        <v>0</v>
+      </c>
+      <c r="W82" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X82" s="33" t="n">
         <v>0.8</v>
@@ -8094,7 +8094,7 @@
         <v>0</v>
       </c>
       <c r="AA82" s="31" t="n">
-        <v>202.30164</v>
+        <v>40.22162400000002</v>
       </c>
       <c r="AB82" s="79" t="n">
         <v>1.022199383350463</v>
@@ -8106,10 +8106,10 @@
         <v>0</v>
       </c>
       <c r="AF82" s="31" t="n">
-        <v>204.68</v>
+        <v>41.51999999999998</v>
       </c>
       <c r="AG82" s="32" t="n">
-        <v>1.006293018682399</v>
+        <v>1.026706231454006</v>
       </c>
       <c r="AH82" s="33" t="n">
         <v>0.8</v>
@@ -8120,10 +8120,10 @@
     </row>
     <row r="83">
       <c r="L83" s="31" t="n">
-        <v>129.649</v>
-      </c>
-      <c r="M83" s="79" t="n">
-        <v>1.02497430626927</v>
+        <v>0</v>
+      </c>
+      <c r="M83" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N83" s="33" t="n">
         <v>0.9</v>
@@ -8132,10 +8132,10 @@
         <v>0</v>
       </c>
       <c r="Q83" s="31" t="n">
-        <v>157.7728600000001</v>
-      </c>
-      <c r="R83" s="79" t="n">
-        <v>1.024974306269271</v>
+        <v>0</v>
+      </c>
+      <c r="R83" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S83" s="33" t="n">
         <v>0.9</v>
@@ -8144,10 +8144,10 @@
         <v>0</v>
       </c>
       <c r="V83" s="31" t="n">
-        <v>199.4599999999999</v>
-      </c>
-      <c r="W83" s="79" t="n">
-        <v>1.02497430626927</v>
+        <v>0</v>
+      </c>
+      <c r="W83" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X83" s="33" t="n">
         <v>0.9</v>
@@ -8156,7 +8156,7 @@
         <v>0</v>
       </c>
       <c r="AA83" s="31" t="n">
-        <v>202.8508200000001</v>
+        <v>40.33081200000002</v>
       </c>
       <c r="AB83" s="79" t="n">
         <v>1.024974306269271</v>
@@ -8168,10 +8168,10 @@
         <v>0</v>
       </c>
       <c r="AF83" s="31" t="n">
-        <v>204.84</v>
+        <v>41.65499999999998</v>
       </c>
       <c r="AG83" s="32" t="n">
-        <v>1.007079646017699</v>
+        <v>1.030044510385756</v>
       </c>
       <c r="AH83" s="33" t="n">
         <v>0.9</v>
@@ -8182,10 +8182,10 @@
     </row>
     <row r="84">
       <c r="L84" s="78" t="n">
-        <v>130</v>
-      </c>
-      <c r="M84" s="79" t="n">
-        <v>1.027749229188078</v>
+        <v>0</v>
+      </c>
+      <c r="M84" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N84" s="41" t="n">
         <v>1</v>
@@ -8194,10 +8194,10 @@
         <v>0</v>
       </c>
       <c r="Q84" s="78" t="n">
-        <v>158.2</v>
-      </c>
-      <c r="R84" s="79" t="n">
-        <v>1.027749229188078</v>
+        <v>0</v>
+      </c>
+      <c r="R84" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="S84" s="41" t="n">
         <v>1</v>
@@ -8206,10 +8206,10 @@
         <v>0</v>
       </c>
       <c r="V84" s="78" t="n">
-        <v>200</v>
-      </c>
-      <c r="W84" s="79" t="n">
-        <v>1.027749229188078</v>
+        <v>0</v>
+      </c>
+      <c r="W84" s="79" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="X84" s="41" t="n">
         <v>1</v>
@@ -8218,7 +8218,7 @@
         <v>0</v>
       </c>
       <c r="AA84" s="78" t="n">
-        <v>203.4</v>
+        <v>40.44</v>
       </c>
       <c r="AB84" s="79" t="n">
         <v>1.027749229188078</v>
@@ -8230,10 +8230,10 @@
         <v>0</v>
       </c>
       <c r="AF84" s="78" t="n">
-        <v>205</v>
+        <v>41.79</v>
       </c>
       <c r="AG84" s="81" t="n">
-        <v>1.007866273352999</v>
+        <v>1.033382789317507</v>
       </c>
       <c r="AH84" s="41" t="n">
         <v>1</v>
@@ -37336,10 +37336,10 @@
         <v>0</v>
       </c>
       <c r="Q4" s="204" t="n">
-        <v>1.182051282051282</v>
+        <v>1.282051282051282</v>
       </c>
       <c r="R4" s="210" t="n">
-        <v>0.3546153846153847</v>
+        <v>0.3846153846153847</v>
       </c>
     </row>
     <row r="5">
@@ -37384,10 +37384,10 @@
       <c r="O5" s="202" t="n"/>
       <c r="P5" s="202" t="n"/>
       <c r="Q5" s="204" t="n">
-        <v>1.002491189694981</v>
+        <v>1.102491189694981</v>
       </c>
       <c r="R5" s="210" t="n">
-        <v>0.3007473569084944</v>
+        <v>0.3307473569084943</v>
       </c>
     </row>
     <row r="6">
@@ -37432,10 +37432,10 @@
       <c r="O6" s="202" t="n"/>
       <c r="P6" s="202" t="n"/>
       <c r="Q6" s="204" t="n">
-        <v>1.184615384615385</v>
+        <v>1.284615384615385</v>
       </c>
       <c r="R6" s="210" t="n">
-        <v>0.3553846153846154</v>
+        <v>0.3853846153846154</v>
       </c>
     </row>
     <row r="7">
@@ -37479,11 +37479,11 @@
       <c r="N7" s="202" t="n"/>
       <c r="O7" s="202" t="n"/>
       <c r="P7" s="202" t="n"/>
-      <c r="Q7" s="206" t="n">
-        <v>0.9884615384615386</v>
+      <c r="Q7" s="204" t="n">
+        <v>1.088461538461539</v>
       </c>
       <c r="R7" s="210" t="n">
-        <v>0.2965384615384616</v>
+        <v>0.3265384615384616</v>
       </c>
     </row>
     <row r="8">
@@ -37528,10 +37528,10 @@
       <c r="O8" s="202" t="n"/>
       <c r="P8" s="202" t="n"/>
       <c r="Q8" s="204" t="n">
-        <v>1.174358974358974</v>
+        <v>1.274358974358974</v>
       </c>
       <c r="R8" s="210" t="n">
-        <v>0.3523076923076923</v>
+        <v>0.3823076923076923</v>
       </c>
     </row>
     <row r="9">
@@ -37576,10 +37576,10 @@
       <c r="O9" s="202" t="n"/>
       <c r="P9" s="202" t="n"/>
       <c r="Q9" s="204" t="n">
-        <v>1.108974358974359</v>
+        <v>1.208974358974359</v>
       </c>
       <c r="R9" s="210" t="n">
-        <v>0.3326923076923077</v>
+        <v>0.3626923076923076</v>
       </c>
     </row>
     <row r="10">
@@ -37624,10 +37624,10 @@
       <c r="O10" s="202" t="n"/>
       <c r="P10" s="202" t="n"/>
       <c r="Q10" s="204" t="n">
-        <v>1.184615384615385</v>
+        <v>1.284615384615385</v>
       </c>
       <c r="R10" s="210" t="n">
-        <v>0.3553846153846154</v>
+        <v>0.3853846153846154</v>
       </c>
     </row>
     <row r="11">
@@ -37676,10 +37676,10 @@
       <c r="O11" s="202" t="n"/>
       <c r="P11" s="202" t="n"/>
       <c r="Q11" s="204" t="n">
-        <v>1.125641025641026</v>
+        <v>1.225641025641026</v>
       </c>
       <c r="R11" s="210" t="n">
-        <v>0.3376923076923077</v>
+        <v>0.3676923076923077</v>
       </c>
     </row>
     <row r="12">
@@ -37723,11 +37723,11 @@
       <c r="N12" s="202" t="n"/>
       <c r="O12" s="202" t="n"/>
       <c r="P12" s="202" t="n"/>
-      <c r="Q12" s="206" t="n">
-        <v>0.9319965973994414</v>
+      <c r="Q12" s="204" t="n">
+        <v>1.031996597399441</v>
       </c>
       <c r="R12" s="210" t="n">
-        <v>0.2795989792198324</v>
+        <v>0.3095989792198324</v>
       </c>
     </row>
     <row r="13">
@@ -37772,10 +37772,10 @@
       <c r="O13" s="202" t="n"/>
       <c r="P13" s="202" t="n"/>
       <c r="Q13" s="204" t="n">
-        <v>1.192307692307692</v>
+        <v>1.292307692307692</v>
       </c>
       <c r="R13" s="210" t="n">
-        <v>0.3576923076923077</v>
+        <v>0.3876923076923077</v>
       </c>
     </row>
     <row r="14">
@@ -37820,10 +37820,10 @@
       <c r="O14" s="202" t="n"/>
       <c r="P14" s="202" t="n"/>
       <c r="Q14" s="204" t="n">
-        <v>1.002491189694981</v>
+        <v>1.102491189694981</v>
       </c>
       <c r="R14" s="210" t="n">
-        <v>0.3007473569084944</v>
+        <v>0.3307473569084943</v>
       </c>
     </row>
     <row r="15">
@@ -37868,10 +37868,10 @@
       <c r="O15" s="202" t="n"/>
       <c r="P15" s="202" t="n"/>
       <c r="Q15" s="206" t="n">
-        <v>0.7897435897435899</v>
+        <v>0.8897435897435898</v>
       </c>
       <c r="R15" s="210" t="n">
-        <v>0.236923076923077</v>
+        <v>0.2669230769230769</v>
       </c>
     </row>
     <row r="16">
@@ -37916,10 +37916,10 @@
       <c r="O16" s="202" t="n"/>
       <c r="P16" s="202" t="n"/>
       <c r="Q16" s="204" t="n">
-        <v>1.042307692307692</v>
+        <v>1.142307692307692</v>
       </c>
       <c r="R16" s="210" t="n">
-        <v>0.3126923076923077</v>
+        <v>0.3426923076923077</v>
       </c>
     </row>
     <row r="17">
@@ -37964,10 +37964,10 @@
       <c r="O17" s="202" t="n"/>
       <c r="P17" s="202" t="n"/>
       <c r="Q17" s="206" t="n">
-        <v>0.851354964151173</v>
+        <v>0.9513549641511728</v>
       </c>
       <c r="R17" s="210" t="n">
-        <v>0.2554064892453519</v>
+        <v>0.2854064892453518</v>
       </c>
     </row>
     <row r="18">
@@ -38012,10 +38012,10 @@
       <c r="O18" s="202" t="n"/>
       <c r="P18" s="202" t="n"/>
       <c r="Q18" s="204" t="n">
-        <v>1.012820512820513</v>
+        <v>1.112820512820513</v>
       </c>
       <c r="R18" s="210" t="n">
-        <v>0.3038461538461538</v>
+        <v>0.3338461538461538</v>
       </c>
     </row>
     <row r="19">
@@ -38060,10 +38060,10 @@
       <c r="O19" s="199" t="n"/>
       <c r="P19" s="199" t="n"/>
       <c r="Q19" s="211" t="n">
-        <v>1.057692307692308</v>
+        <v>1.157692307692308</v>
       </c>
       <c r="R19" s="210" t="n">
-        <v>0.3173076923076923</v>
+        <v>0.3473076923076923</v>
       </c>
     </row>
     <row r="20">
@@ -38076,25 +38076,21 @@
         <v>1.012977411325948</v>
       </c>
       <c r="D20" s="217" t="n">
-        <v>0.05</v>
+        <v>0.09356999635435656</v>
       </c>
       <c r="E20" s="216" t="n">
         <v>0.997896799895361</v>
       </c>
       <c r="F20" s="217" t="n">
-        <v>0.04500000000000001</v>
-      </c>
-      <c r="G20" s="216" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="H20" s="217" t="n">
-        <v>0.285</v>
-      </c>
+        <v>0.07961538461538462</v>
+      </c>
+      <c r="G20" s="218" t="n"/>
+      <c r="H20" s="219" t="n"/>
       <c r="I20" s="216" t="n">
         <v>1.012977411325948</v>
       </c>
       <c r="J20" s="217" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="K20" s="216" t="n">
         <v>0.997896799895361</v>
@@ -38106,12 +38102,8 @@
       <c r="N20" s="219" t="n"/>
       <c r="O20" s="218" t="n"/>
       <c r="P20" s="219" t="n"/>
-      <c r="Q20" s="216" t="n">
-        <v>1.283333333333333</v>
-      </c>
-      <c r="R20" s="217" t="n">
-        <v>0.385</v>
-      </c>
+      <c r="Q20" s="218" t="n"/>
+      <c r="R20" s="219" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">
